--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_nl_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_nl_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>20-07-2021 08:30</t>
+          <t>2021-07-20 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>10-04-2021 08:30</t>
+          <t>2021-10-04 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>10-04-2021 08:30</t>
+          <t>2021-10-04 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>10-04-2021 08:30</t>
+          <t>2021-10-04 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>10-04-2021 08:30</t>
+          <t>2021-10-04 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>10-04-2021 08:30</t>
+          <t>2021-10-04 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>10-04-2021 08:30</t>
+          <t>2021-10-04 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>10-04-2021 08:30</t>
+          <t>2021-10-04 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>10-04-2021 08:30</t>
+          <t>2021-10-04 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>10-04-2021 08:30</t>
+          <t>2021-10-04 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="n">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>18-05-2021 08:30</t>
+          <t>2021-05-18 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>20-07-2021 08:30</t>
+          <t>2021-07-20 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="inlineStr"/>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="inlineStr"/>
